--- a/ADBE_Model.xlsx
+++ b/ADBE_Model.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\OneDrive\Desktop\Equity Research\Models\Technology\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10804967-5F44-4987-9DF2-87A4E7261BB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F37FFD19-0125-4075-BDD1-DA8756428555}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="33390" yWindow="1470" windowWidth="21600" windowHeight="13185" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,6 @@
   <externalReferences>
     <externalReference r:id="rId7"/>
     <externalReference r:id="rId8"/>
-    <externalReference r:id="rId9"/>
   </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
@@ -13863,46 +13862,6 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-      <sheetName val="Notes | Quant Analysis"/>
-      <sheetName val="M&amp;A"/>
-      <sheetName val="Management"/>
-      <sheetName val="Markets | Product Lines"/>
-      <sheetName val="Debt Schedule"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1">
-        <row r="1">
-          <cell r="AW1" t="str">
-            <v>Q1 2020</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="2">
-        <row r="188">
-          <cell r="I188" t="str">
-            <v>Notes:</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
